--- a/Lot Availability.xlsx
+++ b/Lot Availability.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://noblefoodsusa-my.sharepoint.com/personal/mitchell_paliganoff_happyegg_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_E71B4182AB004B0452A4B3D48B78871DBDA81879" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{478B1608-BF57-42A0-80BC-CC42C15362A4}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_E71B4182AB004B0452A4B3D48B78871DBDA81879" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0828CF70-EB83-4833-B9C9-AFB9D062A63B}"/>
   <bookViews>
-    <workbookView xWindow="39530" yWindow="3990" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lot Availability" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId2"/>
+    <pivotCache cacheId="6" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4123" uniqueCount="4123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="3953">
   <si>
     <t>Row Labels</t>
   </si>
@@ -506,51 +506,12 @@
     <t>3019-2382865</t>
   </si>
   <si>
-    <t>3019-2382866</t>
-  </si>
-  <si>
-    <t>3019-2382867</t>
-  </si>
-  <si>
     <t>3019-2382868</t>
   </si>
   <si>
     <t>3019-2403736</t>
   </si>
   <si>
-    <t>3019-2403737</t>
-  </si>
-  <si>
-    <t>3019-2403738</t>
-  </si>
-  <si>
-    <t>3019-2403739</t>
-  </si>
-  <si>
-    <t>3019-2403740</t>
-  </si>
-  <si>
-    <t>3019-2403741</t>
-  </si>
-  <si>
-    <t>3019-2403742</t>
-  </si>
-  <si>
-    <t>3019-2403743</t>
-  </si>
-  <si>
-    <t>3019-2403744</t>
-  </si>
-  <si>
-    <t>3019-2403745</t>
-  </si>
-  <si>
-    <t>3019-2403746</t>
-  </si>
-  <si>
-    <t>3019-2403747</t>
-  </si>
-  <si>
     <t>3019-2403748</t>
   </si>
   <si>
@@ -950,48 +911,6 @@
     <t>3026-2383410</t>
   </si>
   <si>
-    <t>3026-2405636</t>
-  </si>
-  <si>
-    <t>3026-2405637</t>
-  </si>
-  <si>
-    <t>3026-2405638</t>
-  </si>
-  <si>
-    <t>3026-2405639</t>
-  </si>
-  <si>
-    <t>3026-2405640</t>
-  </si>
-  <si>
-    <t>3026-2405641</t>
-  </si>
-  <si>
-    <t>3026-2405642</t>
-  </si>
-  <si>
-    <t>3026-2405643</t>
-  </si>
-  <si>
-    <t>3026-2405644</t>
-  </si>
-  <si>
-    <t>3026-2405645</t>
-  </si>
-  <si>
-    <t>3026-2405646</t>
-  </si>
-  <si>
-    <t>3026-2405647</t>
-  </si>
-  <si>
-    <t>3026-2405648</t>
-  </si>
-  <si>
-    <t>3026-2405649</t>
-  </si>
-  <si>
     <t>3028-2356561</t>
   </si>
   <si>
@@ -1463,54 +1382,6 @@
     <t>3031-2381710</t>
   </si>
   <si>
-    <t>3031-2405067</t>
-  </si>
-  <si>
-    <t>3031-2405068</t>
-  </si>
-  <si>
-    <t>3031-2405069</t>
-  </si>
-  <si>
-    <t>3031-2405070</t>
-  </si>
-  <si>
-    <t>3031-2405071</t>
-  </si>
-  <si>
-    <t>3031-2405072</t>
-  </si>
-  <si>
-    <t>3031-2405073</t>
-  </si>
-  <si>
-    <t>3031-2405074</t>
-  </si>
-  <si>
-    <t>3031-2405075</t>
-  </si>
-  <si>
-    <t>3031-2405076</t>
-  </si>
-  <si>
-    <t>3031-2405077</t>
-  </si>
-  <si>
-    <t>3031-2405078</t>
-  </si>
-  <si>
-    <t>3031-2405079</t>
-  </si>
-  <si>
-    <t>3031-2405080</t>
-  </si>
-  <si>
-    <t>3031-2405081</t>
-  </si>
-  <si>
-    <t>3031-2405082</t>
-  </si>
-  <si>
     <t>3034-2367187</t>
   </si>
   <si>
@@ -1622,42 +1493,6 @@
     <t>3034-2381832</t>
   </si>
   <si>
-    <t>3034-2404587</t>
-  </si>
-  <si>
-    <t>3034-2404588</t>
-  </si>
-  <si>
-    <t>3034-2404589</t>
-  </si>
-  <si>
-    <t>3034-2404590</t>
-  </si>
-  <si>
-    <t>3034-2404591</t>
-  </si>
-  <si>
-    <t>3034-2404592</t>
-  </si>
-  <si>
-    <t>3034-2404593</t>
-  </si>
-  <si>
-    <t>3034-2404594</t>
-  </si>
-  <si>
-    <t>3034-2404595</t>
-  </si>
-  <si>
-    <t>3034-2404596</t>
-  </si>
-  <si>
-    <t>3034-2404597</t>
-  </si>
-  <si>
-    <t>3034-2404598</t>
-  </si>
-  <si>
     <t>3037-2364333</t>
   </si>
   <si>
@@ -2456,63 +2291,6 @@
     <t>3052-2381903</t>
   </si>
   <si>
-    <t>3052-2405083</t>
-  </si>
-  <si>
-    <t>3052-2405084</t>
-  </si>
-  <si>
-    <t>3052-2405085</t>
-  </si>
-  <si>
-    <t>3052-2405086</t>
-  </si>
-  <si>
-    <t>3052-2405087</t>
-  </si>
-  <si>
-    <t>3052-2405088</t>
-  </si>
-  <si>
-    <t>3052-2405089</t>
-  </si>
-  <si>
-    <t>3052-2405090</t>
-  </si>
-  <si>
-    <t>3052-2405091</t>
-  </si>
-  <si>
-    <t>3052-2405092</t>
-  </si>
-  <si>
-    <t>3052-2405093</t>
-  </si>
-  <si>
-    <t>3052-2405094</t>
-  </si>
-  <si>
-    <t>3052-2405095</t>
-  </si>
-  <si>
-    <t>3052-2405096</t>
-  </si>
-  <si>
-    <t>3052-2405097</t>
-  </si>
-  <si>
-    <t>3052-2405098</t>
-  </si>
-  <si>
-    <t>3052-2405099</t>
-  </si>
-  <si>
-    <t>3052-2405100</t>
-  </si>
-  <si>
-    <t>3052-2405101</t>
-  </si>
-  <si>
     <t>3062-2357414</t>
   </si>
   <si>
@@ -4511,84 +4289,9 @@
     <t>3096-2382818</t>
   </si>
   <si>
-    <t>3096-2406010</t>
-  </si>
-  <si>
-    <t>3096-2406011</t>
-  </si>
-  <si>
-    <t>3096-2406012</t>
-  </si>
-  <si>
-    <t>3096-2406013</t>
-  </si>
-  <si>
-    <t>3096-2406014</t>
-  </si>
-  <si>
-    <t>3096-2406015</t>
-  </si>
-  <si>
-    <t>3096-2406016</t>
-  </si>
-  <si>
-    <t>3096-2406017</t>
-  </si>
-  <si>
-    <t>3096-2406018</t>
-  </si>
-  <si>
-    <t>3096-2406019</t>
-  </si>
-  <si>
-    <t>3096-2406020</t>
-  </si>
-  <si>
-    <t>3096-2406021</t>
-  </si>
-  <si>
-    <t>3096-2406022</t>
-  </si>
-  <si>
-    <t>3096-2406023</t>
-  </si>
-  <si>
-    <t>3096-2406024</t>
-  </si>
-  <si>
-    <t>3096-2406025</t>
-  </si>
-  <si>
-    <t>3096-2406026</t>
-  </si>
-  <si>
-    <t>3096-2406027</t>
-  </si>
-  <si>
-    <t>3096-2406028</t>
-  </si>
-  <si>
     <t>3096-2406029</t>
   </si>
   <si>
-    <t>3096-2406030</t>
-  </si>
-  <si>
-    <t>3096-2406031</t>
-  </si>
-  <si>
-    <t>3096-2406032</t>
-  </si>
-  <si>
-    <t>3096-2406033</t>
-  </si>
-  <si>
-    <t>3096-2406034</t>
-  </si>
-  <si>
-    <t>3096-2406035</t>
-  </si>
-  <si>
     <t>3099-2350740</t>
   </si>
   <si>
@@ -8168,81 +7871,6 @@
     <t>3195-2383662</t>
   </si>
   <si>
-    <t>3195-2405682</t>
-  </si>
-  <si>
-    <t>3195-2405683</t>
-  </si>
-  <si>
-    <t>3195-2405684</t>
-  </si>
-  <si>
-    <t>3195-2405685</t>
-  </si>
-  <si>
-    <t>3195-2405686</t>
-  </si>
-  <si>
-    <t>3195-2405687</t>
-  </si>
-  <si>
-    <t>3195-2405688</t>
-  </si>
-  <si>
-    <t>3195-2405689</t>
-  </si>
-  <si>
-    <t>3195-2405690</t>
-  </si>
-  <si>
-    <t>3195-2405691</t>
-  </si>
-  <si>
-    <t>3195-2405692</t>
-  </si>
-  <si>
-    <t>3195-2405693</t>
-  </si>
-  <si>
-    <t>3195-2405694</t>
-  </si>
-  <si>
-    <t>3195-2405695</t>
-  </si>
-  <si>
-    <t>3195-2405696</t>
-  </si>
-  <si>
-    <t>3195-2405697</t>
-  </si>
-  <si>
-    <t>3195-2405698</t>
-  </si>
-  <si>
-    <t>3195-2405699</t>
-  </si>
-  <si>
-    <t>3195-2405700</t>
-  </si>
-  <si>
-    <t>3195-2405701</t>
-  </si>
-  <si>
-    <t>3195-2405702</t>
-  </si>
-  <si>
-    <t>3195-2405703</t>
-  </si>
-  <si>
-    <t>3195-2405704</t>
-  </si>
-  <si>
-    <t>3195-2405705</t>
-  </si>
-  <si>
-    <t>3195-2405706</t>
-  </si>
-  <si>
     <t>3196-2365305</t>
   </si>
   <si>
@@ -10085,9 +9713,6 @@
     <t>3524-2393095</t>
   </si>
   <si>
-    <t>3524-2393096</t>
-  </si>
-  <si>
     <t>3524-2393097</t>
   </si>
   <si>
@@ -10184,69 +9809,6 @@
     <t>3525-2383431</t>
   </si>
   <si>
-    <t>3525-2405722</t>
-  </si>
-  <si>
-    <t>3525-2405723</t>
-  </si>
-  <si>
-    <t>3525-2405724</t>
-  </si>
-  <si>
-    <t>3525-2405725</t>
-  </si>
-  <si>
-    <t>3525-2405726</t>
-  </si>
-  <si>
-    <t>3525-2405727</t>
-  </si>
-  <si>
-    <t>3525-2405728</t>
-  </si>
-  <si>
-    <t>3525-2405729</t>
-  </si>
-  <si>
-    <t>3525-2405730</t>
-  </si>
-  <si>
-    <t>3525-2405731</t>
-  </si>
-  <si>
-    <t>3525-2405732</t>
-  </si>
-  <si>
-    <t>3525-2405733</t>
-  </si>
-  <si>
-    <t>3525-2405734</t>
-  </si>
-  <si>
-    <t>3525-2405735</t>
-  </si>
-  <si>
-    <t>3525-2405736</t>
-  </si>
-  <si>
-    <t>3525-2405737</t>
-  </si>
-  <si>
-    <t>3525-2405738</t>
-  </si>
-  <si>
-    <t>3525-2405739</t>
-  </si>
-  <si>
-    <t>3525-2405740</t>
-  </si>
-  <si>
-    <t>3525-2405741</t>
-  </si>
-  <si>
-    <t>3525-2405742</t>
-  </si>
-  <si>
     <t>3527-2374497</t>
   </si>
   <si>
@@ -10745,15 +10307,6 @@
     <t>3529-2394286</t>
   </si>
   <si>
-    <t>3529-2394287</t>
-  </si>
-  <si>
-    <t>3529-2394288</t>
-  </si>
-  <si>
-    <t>3529-2394289</t>
-  </si>
-  <si>
     <t>3529-2394290</t>
   </si>
   <si>
@@ -10838,76 +10391,13 @@
     <t>3529-2394317</t>
   </si>
   <si>
-    <t>3529-2405223</t>
-  </si>
-  <si>
-    <t>3529-2405224</t>
-  </si>
-  <si>
-    <t>3529-2405225</t>
-  </si>
-  <si>
-    <t>3529-2405226</t>
-  </si>
-  <si>
-    <t>3529-2405227</t>
-  </si>
-  <si>
-    <t>3529-2405228</t>
-  </si>
-  <si>
-    <t>3529-2405229</t>
-  </si>
-  <si>
-    <t>3529-2405230</t>
-  </si>
-  <si>
-    <t>3529-2405231</t>
-  </si>
-  <si>
-    <t>3529-2405232</t>
-  </si>
-  <si>
-    <t>3529-2405233</t>
-  </si>
-  <si>
-    <t>3529-2405234</t>
-  </si>
-  <si>
-    <t>3529-2405235</t>
-  </si>
-  <si>
-    <t>3529-2405236</t>
-  </si>
-  <si>
-    <t>3529-2405237</t>
-  </si>
-  <si>
-    <t>3529-2405238</t>
-  </si>
-  <si>
-    <t>3529-2405239</t>
-  </si>
-  <si>
-    <t>3529-2405240</t>
-  </si>
-  <si>
     <t>3529-2405241</t>
   </si>
   <si>
-    <t>3529-2405242</t>
-  </si>
-  <si>
     <t>3529-2405243</t>
   </si>
   <si>
-    <t>3529-2405244</t>
-  </si>
-  <si>
     <t>3529-2405245</t>
-  </si>
-  <si>
-    <t>3529-2405246</t>
   </si>
   <si>
     <t>3531-2361268</t>
@@ -12957,11 +12447,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Mitchell Paliganoff" refreshedDate="46101.419173379632" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Mitchell Paliganoff" refreshedDate="46104.354755671295" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="1">
     <cacheField name="[Item_Ledger_Entries_Excel].[Lot_No].[Lot_No]" caption="Lot_No" numFmtId="0" hierarchy="9" level="1">
-      <sharedItems count="4121">
+      <sharedItems count="3951">
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3012-2363434]" c="3012-2363434"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3012-2363435]" c="3012-2363435"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3012-2363438]" c="3012-2363438"/>
@@ -13113,21 +12603,8 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2382863]" c="3019-2382863"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2382864]" c="3019-2382864"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2382865]" c="3019-2382865"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2382866]" c="3019-2382866"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2382867]" c="3019-2382867"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2382868]" c="3019-2382868"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403736]" c="3019-2403736"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403737]" c="3019-2403737"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403738]" c="3019-2403738"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403739]" c="3019-2403739"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403740]" c="3019-2403740"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403741]" c="3019-2403741"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403742]" c="3019-2403742"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403743]" c="3019-2403743"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403744]" c="3019-2403744"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403745]" c="3019-2403745"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403746]" c="3019-2403746"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403747]" c="3019-2403747"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3019-2403748]" c="3019-2403748"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3021-2359896]" c="3021-2359896"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3021-2359898]" c="3021-2359898"/>
@@ -13261,20 +12738,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2383408]" c="3026-2383408"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2383409]" c="3026-2383409"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2383410]" c="3026-2383410"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405636]" c="3026-2405636"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405637]" c="3026-2405637"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405638]" c="3026-2405638"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405639]" c="3026-2405639"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405640]" c="3026-2405640"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405641]" c="3026-2405641"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405642]" c="3026-2405642"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405643]" c="3026-2405643"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405644]" c="3026-2405644"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405645]" c="3026-2405645"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405646]" c="3026-2405646"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405647]" c="3026-2405647"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405648]" c="3026-2405648"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3026-2405649]" c="3026-2405649"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3028-2356561]" c="3028-2356561"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3028-2367925]" c="3028-2367925"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3028-2367926]" c="3028-2367926"/>
@@ -13432,22 +12895,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2381708]" c="3031-2381708"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2381709]" c="3031-2381709"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2381710]" c="3031-2381710"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405067]" c="3031-2405067"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405068]" c="3031-2405068"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405069]" c="3031-2405069"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405070]" c="3031-2405070"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405071]" c="3031-2405071"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405072]" c="3031-2405072"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405073]" c="3031-2405073"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405074]" c="3031-2405074"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405075]" c="3031-2405075"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405076]" c="3031-2405076"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405077]" c="3031-2405077"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405078]" c="3031-2405078"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405079]" c="3031-2405079"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405080]" c="3031-2405080"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405081]" c="3031-2405081"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3031-2405082]" c="3031-2405082"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2367187]" c="3034-2367187"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2367189]" c="3034-2367189"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2367190]" c="3034-2367190"/>
@@ -13485,18 +12932,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2381825]" c="3034-2381825"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2381826]" c="3034-2381826"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2381832]" c="3034-2381832"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404587]" c="3034-2404587"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404588]" c="3034-2404588"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404589]" c="3034-2404589"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404590]" c="3034-2404590"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404591]" c="3034-2404591"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404592]" c="3034-2404592"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404593]" c="3034-2404593"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404594]" c="3034-2404594"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404595]" c="3034-2404595"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404596]" c="3034-2404596"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404597]" c="3034-2404597"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3034-2404598]" c="3034-2404598"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3037-2364333]" c="3037-2364333"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3037-2377734]" c="3037-2377734"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3037-2377735]" c="3037-2377735"/>
@@ -13763,25 +13198,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2381901]" c="3052-2381901"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2381902]" c="3052-2381902"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2381903]" c="3052-2381903"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405083]" c="3052-2405083"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405084]" c="3052-2405084"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405085]" c="3052-2405085"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405086]" c="3052-2405086"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405087]" c="3052-2405087"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405088]" c="3052-2405088"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405089]" c="3052-2405089"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405090]" c="3052-2405090"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405091]" c="3052-2405091"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405092]" c="3052-2405092"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405093]" c="3052-2405093"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405094]" c="3052-2405094"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405095]" c="3052-2405095"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405096]" c="3052-2405096"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405097]" c="3052-2405097"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405098]" c="3052-2405098"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405099]" c="3052-2405099"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405100]" c="3052-2405100"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3052-2405101]" c="3052-2405101"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3062-2357414]" c="3062-2357414"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3062-2357415]" c="3062-2357415"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3062-2357416]" c="3062-2357416"/>
@@ -14448,32 +13864,7 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2382816]" c="3096-2382816"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2382817]" c="3096-2382817"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2382818]" c="3096-2382818"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406010]" c="3096-2406010"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406011]" c="3096-2406011"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406012]" c="3096-2406012"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406013]" c="3096-2406013"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406014]" c="3096-2406014"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406015]" c="3096-2406015"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406016]" c="3096-2406016"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406017]" c="3096-2406017"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406018]" c="3096-2406018"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406019]" c="3096-2406019"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406020]" c="3096-2406020"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406021]" c="3096-2406021"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406022]" c="3096-2406022"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406023]" c="3096-2406023"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406024]" c="3096-2406024"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406025]" c="3096-2406025"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406026]" c="3096-2406026"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406027]" c="3096-2406027"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406028]" c="3096-2406028"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406029]" c="3096-2406029"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406030]" c="3096-2406030"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406031]" c="3096-2406031"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406032]" c="3096-2406032"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406033]" c="3096-2406033"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406034]" c="3096-2406034"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3096-2406035]" c="3096-2406035"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3099-2350740]" c="3099-2350740"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3099-2350742]" c="3099-2350742"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3099-2350743]" c="3099-2350743"/>
@@ -15667,31 +15058,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2383660]" c="3195-2383660"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2383661]" c="3195-2383661"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2383662]" c="3195-2383662"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405682]" c="3195-2405682"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405683]" c="3195-2405683"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405684]" c="3195-2405684"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405685]" c="3195-2405685"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405686]" c="3195-2405686"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405687]" c="3195-2405687"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405688]" c="3195-2405688"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405689]" c="3195-2405689"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405690]" c="3195-2405690"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405691]" c="3195-2405691"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405692]" c="3195-2405692"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405693]" c="3195-2405693"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405694]" c="3195-2405694"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405695]" c="3195-2405695"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405696]" c="3195-2405696"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405697]" c="3195-2405697"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405698]" c="3195-2405698"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405699]" c="3195-2405699"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405700]" c="3195-2405700"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405701]" c="3195-2405701"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405702]" c="3195-2405702"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405703]" c="3195-2405703"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405704]" c="3195-2405704"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405705]" c="3195-2405705"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3195-2405706]" c="3195-2405706"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3196-2365305]" c="3196-2365305"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3196-2365307]" c="3196-2365307"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3196-2365308]" c="3196-2365308"/>
@@ -16306,7 +15672,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3524-2393093]" c="3524-2393093"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3524-2393094]" c="3524-2393094"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3524-2393095]" c="3524-2393095"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3524-2393096]" c="3524-2393096"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3524-2393097]" c="3524-2393097"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2366712]" c="3525-2366712"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2366713]" c="3525-2366713"/>
@@ -16339,27 +15704,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2383429]" c="3525-2383429"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2383430]" c="3525-2383430"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2383431]" c="3525-2383431"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405722]" c="3525-2405722"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405723]" c="3525-2405723"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405724]" c="3525-2405724"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405725]" c="3525-2405725"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405726]" c="3525-2405726"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405727]" c="3525-2405727"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405728]" c="3525-2405728"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405729]" c="3525-2405729"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405730]" c="3525-2405730"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405731]" c="3525-2405731"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405732]" c="3525-2405732"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405733]" c="3525-2405733"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405734]" c="3525-2405734"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405735]" c="3525-2405735"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405736]" c="3525-2405736"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405737]" c="3525-2405737"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405738]" c="3525-2405738"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405739]" c="3525-2405739"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405740]" c="3525-2405740"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405741]" c="3525-2405741"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3525-2405742]" c="3525-2405742"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3527-2374497]" c="3527-2374497"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3527-2374498]" c="3527-2374498"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3527-2374499]" c="3527-2374499"/>
@@ -16526,9 +15870,6 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2382003]" c="3529-2382003"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2382004]" c="3529-2382004"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394286]" c="3529-2394286"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394287]" c="3529-2394287"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394288]" c="3529-2394288"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394289]" c="3529-2394289"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394290]" c="3529-2394290"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394291]" c="3529-2394291"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394292]" c="3529-2394292"/>
@@ -16557,30 +15898,9 @@
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394315]" c="3529-2394315"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394316]" c="3529-2394316"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2394317]" c="3529-2394317"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405223]" c="3529-2405223"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405224]" c="3529-2405224"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405225]" c="3529-2405225"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405226]" c="3529-2405226"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405227]" c="3529-2405227"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405228]" c="3529-2405228"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405229]" c="3529-2405229"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405230]" c="3529-2405230"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405231]" c="3529-2405231"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405232]" c="3529-2405232"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405233]" c="3529-2405233"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405234]" c="3529-2405234"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405235]" c="3529-2405235"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405236]" c="3529-2405236"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405237]" c="3529-2405237"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405238]" c="3529-2405238"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405239]" c="3529-2405239"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405240]" c="3529-2405240"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405241]" c="3529-2405241"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405242]" c="3529-2405242"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405243]" c="3529-2405243"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405244]" c="3529-2405244"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405245]" c="3529-2405245"/>
-        <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3529-2405246]" c="3529-2405246"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3531-2361268]" c="3531-2361268"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3531-2361269]" c="3531-2361269"/>
         <s v="[Item_Ledger_Entries_Excel].[Lot_No].&amp;[3531-2361271]" c="3531-2361271"/>
@@ -17165,11 +16485,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A1:A4123" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A1:A3953" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="4122">
+      <items count="3952">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -21121,176 +20441,6 @@
         <item x="3948"/>
         <item x="3949"/>
         <item x="3950"/>
-        <item x="3951"/>
-        <item x="3952"/>
-        <item x="3953"/>
-        <item x="3954"/>
-        <item x="3955"/>
-        <item x="3956"/>
-        <item x="3957"/>
-        <item x="3958"/>
-        <item x="3959"/>
-        <item x="3960"/>
-        <item x="3961"/>
-        <item x="3962"/>
-        <item x="3963"/>
-        <item x="3964"/>
-        <item x="3965"/>
-        <item x="3966"/>
-        <item x="3967"/>
-        <item x="3968"/>
-        <item x="3969"/>
-        <item x="3970"/>
-        <item x="3971"/>
-        <item x="3972"/>
-        <item x="3973"/>
-        <item x="3974"/>
-        <item x="3975"/>
-        <item x="3976"/>
-        <item x="3977"/>
-        <item x="3978"/>
-        <item x="3979"/>
-        <item x="3980"/>
-        <item x="3981"/>
-        <item x="3982"/>
-        <item x="3983"/>
-        <item x="3984"/>
-        <item x="3985"/>
-        <item x="3986"/>
-        <item x="3987"/>
-        <item x="3988"/>
-        <item x="3989"/>
-        <item x="3990"/>
-        <item x="3991"/>
-        <item x="3992"/>
-        <item x="3993"/>
-        <item x="3994"/>
-        <item x="3995"/>
-        <item x="3996"/>
-        <item x="3997"/>
-        <item x="3998"/>
-        <item x="3999"/>
-        <item x="4000"/>
-        <item x="4001"/>
-        <item x="4002"/>
-        <item x="4003"/>
-        <item x="4004"/>
-        <item x="4005"/>
-        <item x="4006"/>
-        <item x="4007"/>
-        <item x="4008"/>
-        <item x="4009"/>
-        <item x="4010"/>
-        <item x="4011"/>
-        <item x="4012"/>
-        <item x="4013"/>
-        <item x="4014"/>
-        <item x="4015"/>
-        <item x="4016"/>
-        <item x="4017"/>
-        <item x="4018"/>
-        <item x="4019"/>
-        <item x="4020"/>
-        <item x="4021"/>
-        <item x="4022"/>
-        <item x="4023"/>
-        <item x="4024"/>
-        <item x="4025"/>
-        <item x="4026"/>
-        <item x="4027"/>
-        <item x="4028"/>
-        <item x="4029"/>
-        <item x="4030"/>
-        <item x="4031"/>
-        <item x="4032"/>
-        <item x="4033"/>
-        <item x="4034"/>
-        <item x="4035"/>
-        <item x="4036"/>
-        <item x="4037"/>
-        <item x="4038"/>
-        <item x="4039"/>
-        <item x="4040"/>
-        <item x="4041"/>
-        <item x="4042"/>
-        <item x="4043"/>
-        <item x="4044"/>
-        <item x="4045"/>
-        <item x="4046"/>
-        <item x="4047"/>
-        <item x="4048"/>
-        <item x="4049"/>
-        <item x="4050"/>
-        <item x="4051"/>
-        <item x="4052"/>
-        <item x="4053"/>
-        <item x="4054"/>
-        <item x="4055"/>
-        <item x="4056"/>
-        <item x="4057"/>
-        <item x="4058"/>
-        <item x="4059"/>
-        <item x="4060"/>
-        <item x="4061"/>
-        <item x="4062"/>
-        <item x="4063"/>
-        <item x="4064"/>
-        <item x="4065"/>
-        <item x="4066"/>
-        <item x="4067"/>
-        <item x="4068"/>
-        <item x="4069"/>
-        <item x="4070"/>
-        <item x="4071"/>
-        <item x="4072"/>
-        <item x="4073"/>
-        <item x="4074"/>
-        <item x="4075"/>
-        <item x="4076"/>
-        <item x="4077"/>
-        <item x="4078"/>
-        <item x="4079"/>
-        <item x="4080"/>
-        <item x="4081"/>
-        <item x="4082"/>
-        <item x="4083"/>
-        <item x="4084"/>
-        <item x="4085"/>
-        <item x="4086"/>
-        <item x="4087"/>
-        <item x="4088"/>
-        <item x="4089"/>
-        <item x="4090"/>
-        <item x="4091"/>
-        <item x="4092"/>
-        <item x="4093"/>
-        <item x="4094"/>
-        <item x="4095"/>
-        <item x="4096"/>
-        <item x="4097"/>
-        <item x="4098"/>
-        <item x="4099"/>
-        <item x="4100"/>
-        <item x="4101"/>
-        <item x="4102"/>
-        <item x="4103"/>
-        <item x="4104"/>
-        <item x="4105"/>
-        <item x="4106"/>
-        <item x="4107"/>
-        <item x="4108"/>
-        <item x="4109"/>
-        <item x="4110"/>
-        <item x="4111"/>
-        <item x="4112"/>
-        <item x="4113"/>
-        <item x="4114"/>
-        <item x="4115"/>
-        <item x="4116"/>
-        <item x="4117"/>
-        <item x="4118"/>
-        <item x="4119"/>
-        <item x="4120"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -21298,7 +20448,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="4122">
+  <rowItems count="3952">
     <i>
       <x/>
     </i>
@@ -33151,516 +32301,6 @@
     </i>
     <i>
       <x v="3950"/>
-    </i>
-    <i>
-      <x v="3951"/>
-    </i>
-    <i>
-      <x v="3952"/>
-    </i>
-    <i>
-      <x v="3953"/>
-    </i>
-    <i>
-      <x v="3954"/>
-    </i>
-    <i>
-      <x v="3955"/>
-    </i>
-    <i>
-      <x v="3956"/>
-    </i>
-    <i>
-      <x v="3957"/>
-    </i>
-    <i>
-      <x v="3958"/>
-    </i>
-    <i>
-      <x v="3959"/>
-    </i>
-    <i>
-      <x v="3960"/>
-    </i>
-    <i>
-      <x v="3961"/>
-    </i>
-    <i>
-      <x v="3962"/>
-    </i>
-    <i>
-      <x v="3963"/>
-    </i>
-    <i>
-      <x v="3964"/>
-    </i>
-    <i>
-      <x v="3965"/>
-    </i>
-    <i>
-      <x v="3966"/>
-    </i>
-    <i>
-      <x v="3967"/>
-    </i>
-    <i>
-      <x v="3968"/>
-    </i>
-    <i>
-      <x v="3969"/>
-    </i>
-    <i>
-      <x v="3970"/>
-    </i>
-    <i>
-      <x v="3971"/>
-    </i>
-    <i>
-      <x v="3972"/>
-    </i>
-    <i>
-      <x v="3973"/>
-    </i>
-    <i>
-      <x v="3974"/>
-    </i>
-    <i>
-      <x v="3975"/>
-    </i>
-    <i>
-      <x v="3976"/>
-    </i>
-    <i>
-      <x v="3977"/>
-    </i>
-    <i>
-      <x v="3978"/>
-    </i>
-    <i>
-      <x v="3979"/>
-    </i>
-    <i>
-      <x v="3980"/>
-    </i>
-    <i>
-      <x v="3981"/>
-    </i>
-    <i>
-      <x v="3982"/>
-    </i>
-    <i>
-      <x v="3983"/>
-    </i>
-    <i>
-      <x v="3984"/>
-    </i>
-    <i>
-      <x v="3985"/>
-    </i>
-    <i>
-      <x v="3986"/>
-    </i>
-    <i>
-      <x v="3987"/>
-    </i>
-    <i>
-      <x v="3988"/>
-    </i>
-    <i>
-      <x v="3989"/>
-    </i>
-    <i>
-      <x v="3990"/>
-    </i>
-    <i>
-      <x v="3991"/>
-    </i>
-    <i>
-      <x v="3992"/>
-    </i>
-    <i>
-      <x v="3993"/>
-    </i>
-    <i>
-      <x v="3994"/>
-    </i>
-    <i>
-      <x v="3995"/>
-    </i>
-    <i>
-      <x v="3996"/>
-    </i>
-    <i>
-      <x v="3997"/>
-    </i>
-    <i>
-      <x v="3998"/>
-    </i>
-    <i>
-      <x v="3999"/>
-    </i>
-    <i>
-      <x v="4000"/>
-    </i>
-    <i>
-      <x v="4001"/>
-    </i>
-    <i>
-      <x v="4002"/>
-    </i>
-    <i>
-      <x v="4003"/>
-    </i>
-    <i>
-      <x v="4004"/>
-    </i>
-    <i>
-      <x v="4005"/>
-    </i>
-    <i>
-      <x v="4006"/>
-    </i>
-    <i>
-      <x v="4007"/>
-    </i>
-    <i>
-      <x v="4008"/>
-    </i>
-    <i>
-      <x v="4009"/>
-    </i>
-    <i>
-      <x v="4010"/>
-    </i>
-    <i>
-      <x v="4011"/>
-    </i>
-    <i>
-      <x v="4012"/>
-    </i>
-    <i>
-      <x v="4013"/>
-    </i>
-    <i>
-      <x v="4014"/>
-    </i>
-    <i>
-      <x v="4015"/>
-    </i>
-    <i>
-      <x v="4016"/>
-    </i>
-    <i>
-      <x v="4017"/>
-    </i>
-    <i>
-      <x v="4018"/>
-    </i>
-    <i>
-      <x v="4019"/>
-    </i>
-    <i>
-      <x v="4020"/>
-    </i>
-    <i>
-      <x v="4021"/>
-    </i>
-    <i>
-      <x v="4022"/>
-    </i>
-    <i>
-      <x v="4023"/>
-    </i>
-    <i>
-      <x v="4024"/>
-    </i>
-    <i>
-      <x v="4025"/>
-    </i>
-    <i>
-      <x v="4026"/>
-    </i>
-    <i>
-      <x v="4027"/>
-    </i>
-    <i>
-      <x v="4028"/>
-    </i>
-    <i>
-      <x v="4029"/>
-    </i>
-    <i>
-      <x v="4030"/>
-    </i>
-    <i>
-      <x v="4031"/>
-    </i>
-    <i>
-      <x v="4032"/>
-    </i>
-    <i>
-      <x v="4033"/>
-    </i>
-    <i>
-      <x v="4034"/>
-    </i>
-    <i>
-      <x v="4035"/>
-    </i>
-    <i>
-      <x v="4036"/>
-    </i>
-    <i>
-      <x v="4037"/>
-    </i>
-    <i>
-      <x v="4038"/>
-    </i>
-    <i>
-      <x v="4039"/>
-    </i>
-    <i>
-      <x v="4040"/>
-    </i>
-    <i>
-      <x v="4041"/>
-    </i>
-    <i>
-      <x v="4042"/>
-    </i>
-    <i>
-      <x v="4043"/>
-    </i>
-    <i>
-      <x v="4044"/>
-    </i>
-    <i>
-      <x v="4045"/>
-    </i>
-    <i>
-      <x v="4046"/>
-    </i>
-    <i>
-      <x v="4047"/>
-    </i>
-    <i>
-      <x v="4048"/>
-    </i>
-    <i>
-      <x v="4049"/>
-    </i>
-    <i>
-      <x v="4050"/>
-    </i>
-    <i>
-      <x v="4051"/>
-    </i>
-    <i>
-      <x v="4052"/>
-    </i>
-    <i>
-      <x v="4053"/>
-    </i>
-    <i>
-      <x v="4054"/>
-    </i>
-    <i>
-      <x v="4055"/>
-    </i>
-    <i>
-      <x v="4056"/>
-    </i>
-    <i>
-      <x v="4057"/>
-    </i>
-    <i>
-      <x v="4058"/>
-    </i>
-    <i>
-      <x v="4059"/>
-    </i>
-    <i>
-      <x v="4060"/>
-    </i>
-    <i>
-      <x v="4061"/>
-    </i>
-    <i>
-      <x v="4062"/>
-    </i>
-    <i>
-      <x v="4063"/>
-    </i>
-    <i>
-      <x v="4064"/>
-    </i>
-    <i>
-      <x v="4065"/>
-    </i>
-    <i>
-      <x v="4066"/>
-    </i>
-    <i>
-      <x v="4067"/>
-    </i>
-    <i>
-      <x v="4068"/>
-    </i>
-    <i>
-      <x v="4069"/>
-    </i>
-    <i>
-      <x v="4070"/>
-    </i>
-    <i>
-      <x v="4071"/>
-    </i>
-    <i>
-      <x v="4072"/>
-    </i>
-    <i>
-      <x v="4073"/>
-    </i>
-    <i>
-      <x v="4074"/>
-    </i>
-    <i>
-      <x v="4075"/>
-    </i>
-    <i>
-      <x v="4076"/>
-    </i>
-    <i>
-      <x v="4077"/>
-    </i>
-    <i>
-      <x v="4078"/>
-    </i>
-    <i>
-      <x v="4079"/>
-    </i>
-    <i>
-      <x v="4080"/>
-    </i>
-    <i>
-      <x v="4081"/>
-    </i>
-    <i>
-      <x v="4082"/>
-    </i>
-    <i>
-      <x v="4083"/>
-    </i>
-    <i>
-      <x v="4084"/>
-    </i>
-    <i>
-      <x v="4085"/>
-    </i>
-    <i>
-      <x v="4086"/>
-    </i>
-    <i>
-      <x v="4087"/>
-    </i>
-    <i>
-      <x v="4088"/>
-    </i>
-    <i>
-      <x v="4089"/>
-    </i>
-    <i>
-      <x v="4090"/>
-    </i>
-    <i>
-      <x v="4091"/>
-    </i>
-    <i>
-      <x v="4092"/>
-    </i>
-    <i>
-      <x v="4093"/>
-    </i>
-    <i>
-      <x v="4094"/>
-    </i>
-    <i>
-      <x v="4095"/>
-    </i>
-    <i>
-      <x v="4096"/>
-    </i>
-    <i>
-      <x v="4097"/>
-    </i>
-    <i>
-      <x v="4098"/>
-    </i>
-    <i>
-      <x v="4099"/>
-    </i>
-    <i>
-      <x v="4100"/>
-    </i>
-    <i>
-      <x v="4101"/>
-    </i>
-    <i>
-      <x v="4102"/>
-    </i>
-    <i>
-      <x v="4103"/>
-    </i>
-    <i>
-      <x v="4104"/>
-    </i>
-    <i>
-      <x v="4105"/>
-    </i>
-    <i>
-      <x v="4106"/>
-    </i>
-    <i>
-      <x v="4107"/>
-    </i>
-    <i>
-      <x v="4108"/>
-    </i>
-    <i>
-      <x v="4109"/>
-    </i>
-    <i>
-      <x v="4110"/>
-    </i>
-    <i>
-      <x v="4111"/>
-    </i>
-    <i>
-      <x v="4112"/>
-    </i>
-    <i>
-      <x v="4113"/>
-    </i>
-    <i>
-      <x v="4114"/>
-    </i>
-    <i>
-      <x v="4115"/>
-    </i>
-    <i>
-      <x v="4116"/>
-    </i>
-    <i>
-      <x v="4117"/>
-    </i>
-    <i>
-      <x v="4118"/>
-    </i>
-    <i>
-      <x v="4119"/>
-    </i>
-    <i>
-      <x v="4120"/>
     </i>
     <i t="grand">
       <x/>
@@ -34022,7 +32662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X4123"/>
+  <dimension ref="A1:X3953"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
@@ -53795,856 +52435,6 @@
         <v>3952</v>
       </c>
     </row>
-    <row r="3954" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3954" s="2" t="s">
-        <v>3953</v>
-      </c>
-    </row>
-    <row r="3955" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3955" s="2" t="s">
-        <v>3954</v>
-      </c>
-    </row>
-    <row r="3956" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3956" s="2" t="s">
-        <v>3955</v>
-      </c>
-    </row>
-    <row r="3957" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3957" s="2" t="s">
-        <v>3956</v>
-      </c>
-    </row>
-    <row r="3958" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3958" s="2" t="s">
-        <v>3957</v>
-      </c>
-    </row>
-    <row r="3959" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3959" s="2" t="s">
-        <v>3958</v>
-      </c>
-    </row>
-    <row r="3960" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3960" s="2" t="s">
-        <v>3959</v>
-      </c>
-    </row>
-    <row r="3961" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3961" s="2" t="s">
-        <v>3960</v>
-      </c>
-    </row>
-    <row r="3962" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3962" s="2" t="s">
-        <v>3961</v>
-      </c>
-    </row>
-    <row r="3963" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3963" s="2" t="s">
-        <v>3962</v>
-      </c>
-    </row>
-    <row r="3964" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3964" s="2" t="s">
-        <v>3963</v>
-      </c>
-    </row>
-    <row r="3965" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3965" s="2" t="s">
-        <v>3964</v>
-      </c>
-    </row>
-    <row r="3966" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3966" s="2" t="s">
-        <v>3965</v>
-      </c>
-    </row>
-    <row r="3967" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3967" s="2" t="s">
-        <v>3966</v>
-      </c>
-    </row>
-    <row r="3968" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3968" s="2" t="s">
-        <v>3967</v>
-      </c>
-    </row>
-    <row r="3969" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3969" s="2" t="s">
-        <v>3968</v>
-      </c>
-    </row>
-    <row r="3970" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3970" s="2" t="s">
-        <v>3969</v>
-      </c>
-    </row>
-    <row r="3971" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3971" s="2" t="s">
-        <v>3970</v>
-      </c>
-    </row>
-    <row r="3972" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3972" s="2" t="s">
-        <v>3971</v>
-      </c>
-    </row>
-    <row r="3973" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3973" s="2" t="s">
-        <v>3972</v>
-      </c>
-    </row>
-    <row r="3974" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3974" s="2" t="s">
-        <v>3973</v>
-      </c>
-    </row>
-    <row r="3975" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3975" s="2" t="s">
-        <v>3974</v>
-      </c>
-    </row>
-    <row r="3976" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3976" s="2" t="s">
-        <v>3975</v>
-      </c>
-    </row>
-    <row r="3977" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3977" s="2" t="s">
-        <v>3976</v>
-      </c>
-    </row>
-    <row r="3978" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3978" s="2" t="s">
-        <v>3977</v>
-      </c>
-    </row>
-    <row r="3979" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3979" s="2" t="s">
-        <v>3978</v>
-      </c>
-    </row>
-    <row r="3980" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3980" s="2" t="s">
-        <v>3979</v>
-      </c>
-    </row>
-    <row r="3981" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3981" s="2" t="s">
-        <v>3980</v>
-      </c>
-    </row>
-    <row r="3982" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3982" s="2" t="s">
-        <v>3981</v>
-      </c>
-    </row>
-    <row r="3983" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3983" s="2" t="s">
-        <v>3982</v>
-      </c>
-    </row>
-    <row r="3984" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3984" s="2" t="s">
-        <v>3983</v>
-      </c>
-    </row>
-    <row r="3985" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3985" s="2" t="s">
-        <v>3984</v>
-      </c>
-    </row>
-    <row r="3986" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3986" s="2" t="s">
-        <v>3985</v>
-      </c>
-    </row>
-    <row r="3987" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3987" s="2" t="s">
-        <v>3986</v>
-      </c>
-    </row>
-    <row r="3988" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3988" s="2" t="s">
-        <v>3987</v>
-      </c>
-    </row>
-    <row r="3989" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3989" s="2" t="s">
-        <v>3988</v>
-      </c>
-    </row>
-    <row r="3990" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3990" s="2" t="s">
-        <v>3989</v>
-      </c>
-    </row>
-    <row r="3991" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3991" s="2" t="s">
-        <v>3990</v>
-      </c>
-    </row>
-    <row r="3992" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3992" s="2" t="s">
-        <v>3991</v>
-      </c>
-    </row>
-    <row r="3993" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3993" s="2" t="s">
-        <v>3992</v>
-      </c>
-    </row>
-    <row r="3994" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3994" s="2" t="s">
-        <v>3993</v>
-      </c>
-    </row>
-    <row r="3995" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3995" s="2" t="s">
-        <v>3994</v>
-      </c>
-    </row>
-    <row r="3996" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3996" s="2" t="s">
-        <v>3995</v>
-      </c>
-    </row>
-    <row r="3997" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3997" s="2" t="s">
-        <v>3996</v>
-      </c>
-    </row>
-    <row r="3998" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3998" s="2" t="s">
-        <v>3997</v>
-      </c>
-    </row>
-    <row r="3999" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3999" s="2" t="s">
-        <v>3998</v>
-      </c>
-    </row>
-    <row r="4000" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4000" s="2" t="s">
-        <v>3999</v>
-      </c>
-    </row>
-    <row r="4001" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4001" s="2" t="s">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="4002" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4002" s="2" t="s">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="4003" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4003" s="2" t="s">
-        <v>4002</v>
-      </c>
-    </row>
-    <row r="4004" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4004" s="2" t="s">
-        <v>4003</v>
-      </c>
-    </row>
-    <row r="4005" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4005" s="2" t="s">
-        <v>4004</v>
-      </c>
-    </row>
-    <row r="4006" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4006" s="2" t="s">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="4007" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4007" s="2" t="s">
-        <v>4006</v>
-      </c>
-    </row>
-    <row r="4008" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4008" s="2" t="s">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="4009" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4009" s="2" t="s">
-        <v>4008</v>
-      </c>
-    </row>
-    <row r="4010" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4010" s="2" t="s">
-        <v>4009</v>
-      </c>
-    </row>
-    <row r="4011" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4011" s="2" t="s">
-        <v>4010</v>
-      </c>
-    </row>
-    <row r="4012" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4012" s="2" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="4013" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4013" s="2" t="s">
-        <v>4012</v>
-      </c>
-    </row>
-    <row r="4014" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4014" s="2" t="s">
-        <v>4013</v>
-      </c>
-    </row>
-    <row r="4015" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4015" s="2" t="s">
-        <v>4014</v>
-      </c>
-    </row>
-    <row r="4016" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4016" s="2" t="s">
-        <v>4015</v>
-      </c>
-    </row>
-    <row r="4017" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4017" s="2" t="s">
-        <v>4016</v>
-      </c>
-    </row>
-    <row r="4018" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4018" s="2" t="s">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="4019" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4019" s="2" t="s">
-        <v>4018</v>
-      </c>
-    </row>
-    <row r="4020" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4020" s="2" t="s">
-        <v>4019</v>
-      </c>
-    </row>
-    <row r="4021" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4021" s="2" t="s">
-        <v>4020</v>
-      </c>
-    </row>
-    <row r="4022" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4022" s="2" t="s">
-        <v>4021</v>
-      </c>
-    </row>
-    <row r="4023" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4023" s="2" t="s">
-        <v>4022</v>
-      </c>
-    </row>
-    <row r="4024" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4024" s="2" t="s">
-        <v>4023</v>
-      </c>
-    </row>
-    <row r="4025" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4025" s="2" t="s">
-        <v>4024</v>
-      </c>
-    </row>
-    <row r="4026" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4026" s="2" t="s">
-        <v>4025</v>
-      </c>
-    </row>
-    <row r="4027" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4027" s="2" t="s">
-        <v>4026</v>
-      </c>
-    </row>
-    <row r="4028" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4028" s="2" t="s">
-        <v>4027</v>
-      </c>
-    </row>
-    <row r="4029" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4029" s="2" t="s">
-        <v>4028</v>
-      </c>
-    </row>
-    <row r="4030" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4030" s="2" t="s">
-        <v>4029</v>
-      </c>
-    </row>
-    <row r="4031" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4031" s="2" t="s">
-        <v>4030</v>
-      </c>
-    </row>
-    <row r="4032" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4032" s="2" t="s">
-        <v>4031</v>
-      </c>
-    </row>
-    <row r="4033" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4033" s="2" t="s">
-        <v>4032</v>
-      </c>
-    </row>
-    <row r="4034" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4034" s="2" t="s">
-        <v>4033</v>
-      </c>
-    </row>
-    <row r="4035" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4035" s="2" t="s">
-        <v>4034</v>
-      </c>
-    </row>
-    <row r="4036" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4036" s="2" t="s">
-        <v>4035</v>
-      </c>
-    </row>
-    <row r="4037" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4037" s="2" t="s">
-        <v>4036</v>
-      </c>
-    </row>
-    <row r="4038" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4038" s="2" t="s">
-        <v>4037</v>
-      </c>
-    </row>
-    <row r="4039" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4039" s="2" t="s">
-        <v>4038</v>
-      </c>
-    </row>
-    <row r="4040" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4040" s="2" t="s">
-        <v>4039</v>
-      </c>
-    </row>
-    <row r="4041" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4041" s="2" t="s">
-        <v>4040</v>
-      </c>
-    </row>
-    <row r="4042" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4042" s="2" t="s">
-        <v>4041</v>
-      </c>
-    </row>
-    <row r="4043" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4043" s="2" t="s">
-        <v>4042</v>
-      </c>
-    </row>
-    <row r="4044" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4044" s="2" t="s">
-        <v>4043</v>
-      </c>
-    </row>
-    <row r="4045" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4045" s="2" t="s">
-        <v>4044</v>
-      </c>
-    </row>
-    <row r="4046" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4046" s="2" t="s">
-        <v>4045</v>
-      </c>
-    </row>
-    <row r="4047" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4047" s="2" t="s">
-        <v>4046</v>
-      </c>
-    </row>
-    <row r="4048" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4048" s="2" t="s">
-        <v>4047</v>
-      </c>
-    </row>
-    <row r="4049" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4049" s="2" t="s">
-        <v>4048</v>
-      </c>
-    </row>
-    <row r="4050" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4050" s="2" t="s">
-        <v>4049</v>
-      </c>
-    </row>
-    <row r="4051" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4051" s="2" t="s">
-        <v>4050</v>
-      </c>
-    </row>
-    <row r="4052" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4052" s="2" t="s">
-        <v>4051</v>
-      </c>
-    </row>
-    <row r="4053" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4053" s="2" t="s">
-        <v>4052</v>
-      </c>
-    </row>
-    <row r="4054" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4054" s="2" t="s">
-        <v>4053</v>
-      </c>
-    </row>
-    <row r="4055" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4055" s="2" t="s">
-        <v>4054</v>
-      </c>
-    </row>
-    <row r="4056" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4056" s="2" t="s">
-        <v>4055</v>
-      </c>
-    </row>
-    <row r="4057" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4057" s="2" t="s">
-        <v>4056</v>
-      </c>
-    </row>
-    <row r="4058" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4058" s="2" t="s">
-        <v>4057</v>
-      </c>
-    </row>
-    <row r="4059" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4059" s="2" t="s">
-        <v>4058</v>
-      </c>
-    </row>
-    <row r="4060" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4060" s="2" t="s">
-        <v>4059</v>
-      </c>
-    </row>
-    <row r="4061" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4061" s="2" t="s">
-        <v>4060</v>
-      </c>
-    </row>
-    <row r="4062" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4062" s="2" t="s">
-        <v>4061</v>
-      </c>
-    </row>
-    <row r="4063" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4063" s="2" t="s">
-        <v>4062</v>
-      </c>
-    </row>
-    <row r="4064" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4064" s="2" t="s">
-        <v>4063</v>
-      </c>
-    </row>
-    <row r="4065" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4065" s="2" t="s">
-        <v>4064</v>
-      </c>
-    </row>
-    <row r="4066" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4066" s="2" t="s">
-        <v>4065</v>
-      </c>
-    </row>
-    <row r="4067" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4067" s="2" t="s">
-        <v>4066</v>
-      </c>
-    </row>
-    <row r="4068" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4068" s="2" t="s">
-        <v>4067</v>
-      </c>
-    </row>
-    <row r="4069" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4069" s="2" t="s">
-        <v>4068</v>
-      </c>
-    </row>
-    <row r="4070" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4070" s="2" t="s">
-        <v>4069</v>
-      </c>
-    </row>
-    <row r="4071" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4071" s="2" t="s">
-        <v>4070</v>
-      </c>
-    </row>
-    <row r="4072" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4072" s="2" t="s">
-        <v>4071</v>
-      </c>
-    </row>
-    <row r="4073" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4073" s="2" t="s">
-        <v>4072</v>
-      </c>
-    </row>
-    <row r="4074" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4074" s="2" t="s">
-        <v>4073</v>
-      </c>
-    </row>
-    <row r="4075" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4075" s="2" t="s">
-        <v>4074</v>
-      </c>
-    </row>
-    <row r="4076" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4076" s="2" t="s">
-        <v>4075</v>
-      </c>
-    </row>
-    <row r="4077" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4077" s="2" t="s">
-        <v>4076</v>
-      </c>
-    </row>
-    <row r="4078" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4078" s="2" t="s">
-        <v>4077</v>
-      </c>
-    </row>
-    <row r="4079" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4079" s="2" t="s">
-        <v>4078</v>
-      </c>
-    </row>
-    <row r="4080" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4080" s="2" t="s">
-        <v>4079</v>
-      </c>
-    </row>
-    <row r="4081" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4081" s="2" t="s">
-        <v>4080</v>
-      </c>
-    </row>
-    <row r="4082" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4082" s="2" t="s">
-        <v>4081</v>
-      </c>
-    </row>
-    <row r="4083" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4083" s="2" t="s">
-        <v>4082</v>
-      </c>
-    </row>
-    <row r="4084" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4084" s="2" t="s">
-        <v>4083</v>
-      </c>
-    </row>
-    <row r="4085" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4085" s="2" t="s">
-        <v>4084</v>
-      </c>
-    </row>
-    <row r="4086" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4086" s="2" t="s">
-        <v>4085</v>
-      </c>
-    </row>
-    <row r="4087" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4087" s="2" t="s">
-        <v>4086</v>
-      </c>
-    </row>
-    <row r="4088" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4088" s="2" t="s">
-        <v>4087</v>
-      </c>
-    </row>
-    <row r="4089" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4089" s="2" t="s">
-        <v>4088</v>
-      </c>
-    </row>
-    <row r="4090" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4090" s="2" t="s">
-        <v>4089</v>
-      </c>
-    </row>
-    <row r="4091" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4091" s="2" t="s">
-        <v>4090</v>
-      </c>
-    </row>
-    <row r="4092" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4092" s="2" t="s">
-        <v>4091</v>
-      </c>
-    </row>
-    <row r="4093" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4093" s="2" t="s">
-        <v>4092</v>
-      </c>
-    </row>
-    <row r="4094" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4094" s="2" t="s">
-        <v>4093</v>
-      </c>
-    </row>
-    <row r="4095" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4095" s="2" t="s">
-        <v>4094</v>
-      </c>
-    </row>
-    <row r="4096" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4096" s="2" t="s">
-        <v>4095</v>
-      </c>
-    </row>
-    <row r="4097" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4097" s="2" t="s">
-        <v>4096</v>
-      </c>
-    </row>
-    <row r="4098" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4098" s="2" t="s">
-        <v>4097</v>
-      </c>
-    </row>
-    <row r="4099" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4099" s="2" t="s">
-        <v>4098</v>
-      </c>
-    </row>
-    <row r="4100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4100" s="2" t="s">
-        <v>4099</v>
-      </c>
-    </row>
-    <row r="4101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4101" s="2" t="s">
-        <v>4100</v>
-      </c>
-    </row>
-    <row r="4102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4102" s="2" t="s">
-        <v>4101</v>
-      </c>
-    </row>
-    <row r="4103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4103" s="2" t="s">
-        <v>4102</v>
-      </c>
-    </row>
-    <row r="4104" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4104" s="2" t="s">
-        <v>4103</v>
-      </c>
-    </row>
-    <row r="4105" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4105" s="2" t="s">
-        <v>4104</v>
-      </c>
-    </row>
-    <row r="4106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4106" s="2" t="s">
-        <v>4105</v>
-      </c>
-    </row>
-    <row r="4107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4107" s="2" t="s">
-        <v>4106</v>
-      </c>
-    </row>
-    <row r="4108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4108" s="2" t="s">
-        <v>4107</v>
-      </c>
-    </row>
-    <row r="4109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4109" s="2" t="s">
-        <v>4108</v>
-      </c>
-    </row>
-    <row r="4110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4110" s="2" t="s">
-        <v>4109</v>
-      </c>
-    </row>
-    <row r="4111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4111" s="2" t="s">
-        <v>4110</v>
-      </c>
-    </row>
-    <row r="4112" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4112" s="2" t="s">
-        <v>4111</v>
-      </c>
-    </row>
-    <row r="4113" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4113" s="2" t="s">
-        <v>4112</v>
-      </c>
-    </row>
-    <row r="4114" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4114" s="2" t="s">
-        <v>4113</v>
-      </c>
-    </row>
-    <row r="4115" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4115" s="2" t="s">
-        <v>4114</v>
-      </c>
-    </row>
-    <row r="4116" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4116" s="2" t="s">
-        <v>4115</v>
-      </c>
-    </row>
-    <row r="4117" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4117" s="2" t="s">
-        <v>4116</v>
-      </c>
-    </row>
-    <row r="4118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4118" s="2" t="s">
-        <v>4117</v>
-      </c>
-    </row>
-    <row r="4119" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4119" s="2" t="s">
-        <v>4118</v>
-      </c>
-    </row>
-    <row r="4120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4120" s="2" t="s">
-        <v>4119</v>
-      </c>
-    </row>
-    <row r="4121" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4121" s="2" t="s">
-        <v>4120</v>
-      </c>
-    </row>
-    <row r="4122" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4122" s="2" t="s">
-        <v>4121</v>
-      </c>
-    </row>
-    <row r="4123" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4123" s="2" t="s">
-        <v>4122</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
